--- a/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Communication.xlsx
+++ b/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Communication.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$51</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1826" uniqueCount="388">
   <si>
     <t>Property</t>
   </si>
@@ -120,7 +120,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Communication</t>
+    <t>https://gematik.de/fhir/tiflow/StructureDefinition/tiflow-communication</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -326,13 +326,197 @@
 </t>
   </si>
   <si>
-    <t>Communication.implicitRules</t>
+    <t>Communication.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Communication.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Communication.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>Communication.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>Communication.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>Communication.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>Communication.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>Communication.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Communication.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -428,28 +612,10 @@
     <t>Communication.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Communication.modifierExtension</t>
@@ -493,6 +659,9 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
+    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
+  </si>
+  <si>
     <t>Communication.instantiatesCanonical</t>
   </si>
   <si>
@@ -506,6 +675,9 @@
     <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Communication.</t>
   </si>
   <si>
+    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
+  </si>
+  <si>
     <t>Event.instantiatesCanonical</t>
   </si>
   <si>
@@ -547,45 +719,20 @@
     <t>Hat die Form 'Task/{{PrescriptionID}}'</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
     <t>Event.basedOn</t>
   </si>
   <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
+  </si>
+  <si>
     <t>Communication.basedOn.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Communication.basedOn.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Communication.basedOn.reference</t>
@@ -612,9 +759,6 @@
   </si>
   <si>
     <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
@@ -679,6 +823,9 @@
     <t>Part of this action.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
     <t>Event.partOf</t>
   </si>
   <si>
@@ -745,9 +892,6 @@
     <t>This is generally only used for "exception" statuses such as "not-done", "suspended" or "aborted". The reason for performing the event at all is captured in reasonCode, not here.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
     <t>Codes for the reason why a communication did not happen.</t>
   </si>
   <si>
@@ -757,6 +901,9 @@
     <t>Event.statusReason</t>
   </si>
   <si>
+    <t>CD</t>
+  </si>
+  <si>
     <t>Communication.category</t>
   </si>
   <si>
@@ -809,6 +956,9 @@
   </si>
   <si>
     <t>A channel that was used for this communication (e.g. email, fax).</t>
+  </si>
+  <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>Codes for communication mediums such as phone, fax, email, in person, etc.</t>
@@ -905,7 +1055,7 @@
     <t>The time when this communication was sent.</t>
   </si>
   <si>
-    <t>Wird vom E-Rezept-Server gesetzt. Ein Client hat diesen Wert daher immer verfügbar.</t>
+    <t>Wird vom TIFlow-Server gesetzt. Ein Client hat diesen Wert daher immer verfügbar.</t>
   </si>
   <si>
     <t>Event.occurrence[x] {Invariant: maps to period.start}</t>
@@ -958,11 +1108,11 @@
     <t>Die Entität (z. B. Person, Organisation), die Quelle der Kommunikation war.</t>
   </si>
   <si>
-    <t>Nachrichtenabsender — wird vom E-Rezept-Server unter Verwendung der AuthN-Credential des Clients gesetzt.
+    <t>Nachrichtenabsender — wird vom TIFlow-Server gesetzt.
 Die Entität (z. B. Person, Organisation), die Quelle der Kommunikation war.</t>
   </si>
   <si>
-    <t>Wird vom E-Rezept-Server unter Verwendung der AuthN-Credential des Clients gesetzt.</t>
+    <t>Wird vom TIFlow-Server gesetzt.</t>
   </si>
   <si>
     <t>Communication.reasonCode</t>
@@ -1060,9 +1210,6 @@
     <t>A communicated content (or for multi-part communications, one portion of the communication).</t>
   </si>
   <si>
-    <t>Dieser Inhalt muss ein JSON gemäß gemSpec_DM_eRp sein.</t>
-  </si>
-  <si>
     <t>Communication.note</t>
   </si>
   <si>
@@ -1076,7 +1223,13 @@
     <t>Additional notes or commentary about the communication by the sender, receiver or other interested parties.</t>
   </si>
   <si>
+    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
+  </si>
+  <si>
     <t>Event.note</t>
+  </si>
+  <si>
+    <t>Act</t>
   </si>
 </sst>
 </file>
@@ -1397,7 +1550,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM43"/>
+  <dimension ref="A1:AM51"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="34.78125" customWidth="true" bestFit="true"/>
@@ -1424,7 +1577,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="64.65234375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="52.72265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -1437,7 +1590,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="43.421875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="38.5234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="123.23828125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1779,7 +1932,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>95</v>
       </c>
@@ -1798,7 +1951,7 @@
         <v>88</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>78</v>
@@ -1910,10 +2063,10 @@
         <v>78</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>102</v>
@@ -1924,9 +2077,7 @@
       <c r="M5" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>105</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>78</v>
@@ -1975,7 +2126,7 @@
         <v>78</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>79</v>
@@ -1987,7 +2138,7 @@
         <v>78</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>78</v>
@@ -1996,7 +2147,7 @@
         <v>78</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>78</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" hidden="true">
@@ -2008,14 +2159,14 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>78</v>
@@ -2027,16 +2178,16 @@
         <v>78</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2062,43 +2213,43 @@
         <v>78</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="Y6" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AC6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AD6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>78</v>
@@ -2107,19 +2258,19 @@
         <v>78</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>78</v>
+        <v>106</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2129,16 +2280,16 @@
         <v>88</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>119</v>
@@ -2218,47 +2369,47 @@
         <v>78</v>
       </c>
       <c r="AM7" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
         <v>123</v>
       </c>
-    </row>
-    <row r="8" hidden="true">
-      <c r="A8" t="s" s="2">
-        <v>124</v>
-      </c>
       <c r="B8" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>125</v>
+        <v>78</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="M8" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2308,19 +2459,19 @@
         <v>78</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>78</v>
@@ -2329,26 +2480,26 @@
         <v>78</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>131</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>78</v>
@@ -2357,19 +2508,19 @@
         <v>78</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2419,19 +2570,19 @@
         <v>78</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>78</v>
@@ -2440,19 +2591,19 @@
         <v>78</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>131</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2465,26 +2616,24 @@
         <v>78</v>
       </c>
       <c r="I10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J10" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="J10" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K10" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>78</v>
       </c>
@@ -2532,7 +2681,7 @@
         <v>78</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -2544,7 +2693,7 @@
         <v>78</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>78</v>
@@ -2553,15 +2702,15 @@
         <v>78</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>131</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2584,20 +2733,18 @@
         <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>78</v>
       </c>
@@ -2621,13 +2768,13 @@
         <v>78</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>78</v>
@@ -2645,7 +2792,7 @@
         <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -2654,27 +2801,27 @@
         <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="AL11" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AM11" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2685,7 +2832,7 @@
         <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>78</v>
@@ -2697,15 +2844,17 @@
         <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="M12" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>78</v>
@@ -2730,13 +2879,13 @@
         <v>78</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>78</v>
+        <v>158</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>78</v>
@@ -2754,7 +2903,7 @@
         <v>78</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -2763,27 +2912,27 @@
         <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>157</v>
+        <v>78</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2794,28 +2943,28 @@
         <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2865,13 +3014,13 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>78</v>
@@ -2880,41 +3029,41 @@
         <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>163</v>
+        <v>78</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>158</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K14" t="s" s="2">
         <v>166</v>
@@ -2952,13 +3101,13 @@
         <v>78</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>78</v>
@@ -2976,13 +3125,13 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>78</v>
@@ -2991,7 +3140,7 @@
         <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>170</v>
+        <v>78</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>78</v>
@@ -3002,14 +3151,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>78</v>
+        <v>175</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3028,15 +3177,17 @@
         <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>78</v>
@@ -3085,7 +3236,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3097,7 +3248,7 @@
         <v>78</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>78</v>
@@ -3106,19 +3257,19 @@
         <v>78</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>133</v>
+        <v>183</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3137,16 +3288,16 @@
         <v>78</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>134</v>
+        <v>184</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>135</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>137</v>
+        <v>187</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3184,19 +3335,19 @@
         <v>78</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>180</v>
+        <v>78</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3208,7 +3359,7 @@
         <v>78</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>78</v>
@@ -3217,47 +3368,47 @@
         <v>78</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>176</v>
+        <v>189</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>172</v>
+        <v>109</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>167</v>
+        <v>110</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>169</v>
+        <v>112</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3295,31 +3446,31 @@
         <v>78</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>186</v>
+        <v>78</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>78</v>
@@ -3328,49 +3479,51 @@
         <v>78</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>131</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="O18" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>78</v>
       </c>
@@ -3394,43 +3547,43 @@
         <v>78</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>192</v>
+        <v>78</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>193</v>
+        <v>78</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>78</v>
@@ -3439,15 +3592,15 @@
         <v>78</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>131</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3458,7 +3611,7 @@
         <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>78</v>
@@ -3470,18 +3623,20 @@
         <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>146</v>
+        <v>199</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="O19" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>78</v>
       </c>
@@ -3529,36 +3684,36 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>78</v>
+        <v>204</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>78</v>
+        <v>205</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3569,7 +3724,7 @@
         <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>78</v>
@@ -3581,16 +3736,16 @@
         <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>172</v>
+        <v>208</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3640,13 +3795,13 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>78</v>
@@ -3655,25 +3810,25 @@
         <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>131</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3692,15 +3847,17 @@
         <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>208</v>
+        <v>130</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>78</v>
@@ -3749,7 +3906,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3764,52 +3921,54 @@
         <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>78</v>
+        <v>213</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>78</v>
+        <v>220</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>78</v>
@@ -3858,7 +4017,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3867,27 +4026,27 @@
         <v>80</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>78</v>
+        <v>226</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>78</v>
+        <v>227</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3895,39 +4054,37 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>217</v>
+        <v>103</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>219</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>220</v>
+        <v>78</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>78</v>
@@ -3945,13 +4102,13 @@
         <v>78</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>221</v>
+        <v>78</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>222</v>
+        <v>78</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>223</v>
+        <v>78</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>78</v>
@@ -3969,10 +4126,10 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>216</v>
+        <v>105</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>88</v>
@@ -3981,35 +4138,35 @@
         <v>78</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>224</v>
+        <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>225</v>
+        <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>78</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>227</v>
+        <v>108</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>78</v>
@@ -4018,19 +4175,19 @@
         <v>78</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>228</v>
+        <v>109</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>229</v>
+        <v>110</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>230</v>
+        <v>111</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>231</v>
+        <v>112</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4056,60 +4213,60 @@
         <v>78</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>232</v>
+        <v>78</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>233</v>
+        <v>78</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>226</v>
+        <v>116</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>235</v>
+        <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>78</v>
+        <v>106</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4117,31 +4274,31 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>228</v>
+        <v>102</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4167,40 +4324,40 @@
         <v>78</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="Y25" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>236</v>
-      </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>78</v>
+        <v>233</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>100</v>
@@ -4209,18 +4366,18 @@
         <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>242</v>
+        <v>78</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>78</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4231,7 +4388,7 @@
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>78</v>
@@ -4243,24 +4400,22 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q26" t="s" s="2">
-        <v>247</v>
-      </c>
+      <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
         <v>78</v>
       </c>
@@ -4280,13 +4435,13 @@
         <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>221</v>
+        <v>146</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>78</v>
@@ -4304,7 +4459,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4322,18 +4477,18 @@
         <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>250</v>
+        <v>78</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>78</v>
+        <v>189</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4344,7 +4499,7 @@
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>78</v>
@@ -4353,18 +4508,20 @@
         <v>78</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>228</v>
+        <v>199</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -4389,13 +4546,13 @@
         <v>78</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>232</v>
+        <v>78</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>254</v>
+        <v>78</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>255</v>
+        <v>78</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>78</v>
@@ -4413,16 +4570,16 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>100</v>
@@ -4434,26 +4591,26 @@
         <v>78</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>78</v>
+        <v>246</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>257</v>
+        <v>78</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>78</v>
@@ -4465,15 +4622,17 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>258</v>
+        <v>102</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>78</v>
@@ -4522,7 +4681,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4537,25 +4696,25 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>261</v>
+        <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>262</v>
+        <v>78</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>78</v>
+        <v>189</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>78</v>
+        <v>253</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4571,19 +4730,19 @@
         <v>78</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4609,13 +4768,13 @@
         <v>78</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>232</v>
+        <v>78</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>267</v>
+        <v>78</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>268</v>
+        <v>78</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>78</v>
@@ -4633,36 +4792,36 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>78</v>
+        <v>258</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>269</v>
+        <v>78</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>78</v>
+        <v>227</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4685,16 +4844,16 @@
         <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>208</v>
+        <v>260</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4744,7 +4903,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -4753,27 +4912,27 @@
         <v>80</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>269</v>
+        <v>78</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>78</v>
+        <v>227</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4781,31 +4940,31 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>275</v>
+        <v>166</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4813,7 +4972,7 @@
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>78</v>
+        <v>267</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>78</v>
@@ -4831,13 +4990,13 @@
         <v>78</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>78</v>
+        <v>268</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>78</v>
+        <v>269</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>78</v>
+        <v>270</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>78</v>
@@ -4855,10 +5014,10 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>88</v>
@@ -4870,53 +5029,53 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>78</v>
+        <v>274</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J32" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K32" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4942,13 +5101,13 @@
         <v>78</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>78</v>
+        <v>279</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>78</v>
+        <v>280</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>78</v>
@@ -4966,7 +5125,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -4975,27 +5134,27 @@
         <v>88</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>286</v>
+        <v>78</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>78</v>
+        <v>282</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5006,10 +5165,10 @@
         <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>78</v>
@@ -5018,16 +5177,16 @@
         <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5053,13 +5212,13 @@
         <v>78</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>78</v>
+        <v>287</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>78</v>
+        <v>288</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>78</v>
@@ -5077,36 +5236,36 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="34" hidden="true">
+      <c r="A34" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AL33" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="2">
-        <v>291</v>
-      </c>
       <c r="B34" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5117,34 +5276,36 @@
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J34" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I34" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J34" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K34" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q34" s="2"/>
+      <c r="Q34" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="R34" t="s" s="2">
         <v>78</v>
       </c>
@@ -5164,13 +5325,13 @@
         <v>78</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>78</v>
+        <v>268</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>78</v>
+        <v>295</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>78</v>
+        <v>296</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>78</v>
@@ -5188,13 +5349,13 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>78</v>
@@ -5203,7 +5364,7 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>296</v>
+        <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>297</v>
@@ -5212,7 +5373,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>298</v>
       </c>
@@ -5228,10 +5389,10 @@
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>78</v>
@@ -5240,16 +5401,16 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5275,13 +5436,13 @@
         <v>78</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>78</v>
+        <v>302</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>78</v>
+        <v>303</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>78</v>
@@ -5305,34 +5466,34 @@
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>296</v>
+        <v>78</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>297</v>
+        <v>78</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>78</v>
+        <v>282</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>78</v>
+        <v>305</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5351,16 +5512,16 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>228</v>
+        <v>306</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>306</v>
+        <v>257</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5386,13 +5547,13 @@
         <v>78</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>232</v>
+        <v>78</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>307</v>
+        <v>78</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>308</v>
+        <v>78</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>78</v>
@@ -5410,19 +5571,19 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>309</v>
@@ -5431,15 +5592,15 @@
         <v>310</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>311</v>
+        <v>227</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5459,18 +5620,20 @@
         <v>78</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="M37" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -5495,13 +5658,13 @@
         <v>78</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>78</v>
+        <v>315</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>78</v>
+        <v>316</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>78</v>
@@ -5519,31 +5682,31 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>316</v>
+        <v>78</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>317</v>
+        <v>282</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
         <v>318</v>
       </c>
@@ -5559,10 +5722,10 @@
         <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>78</v>
@@ -5571,15 +5734,17 @@
         <v>78</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -5637,19 +5802,19 @@
         <v>80</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>78</v>
+        <v>317</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>78</v>
+        <v>227</v>
       </c>
     </row>
     <row r="39" hidden="true">
@@ -5668,7 +5833,7 @@
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>78</v>
@@ -5677,18 +5842,20 @@
         <v>78</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>172</v>
+        <v>323</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>173</v>
+        <v>324</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -5737,7 +5904,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>175</v>
+        <v>322</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -5746,41 +5913,41 @@
         <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>78</v>
+        <v>225</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>78</v>
+        <v>327</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>78</v>
+        <v>317</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>176</v>
+        <v>227</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>78</v>
@@ -5789,16 +5956,16 @@
         <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>134</v>
+        <v>329</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>135</v>
+        <v>330</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>178</v>
+        <v>331</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>137</v>
+        <v>332</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5848,72 +6015,70 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>182</v>
+        <v>328</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>78</v>
+        <v>333</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>78</v>
+        <v>334</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>176</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>325</v>
+        <v>78</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>134</v>
+        <v>329</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>78</v>
       </c>
@@ -5961,36 +6126,36 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>78</v>
+        <v>338</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>78</v>
+        <v>334</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>131</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5998,13 +6163,13 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>78</v>
@@ -6013,16 +6178,16 @@
         <v>78</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6072,36 +6237,36 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>78</v>
+        <v>344</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>78</v>
+        <v>345</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>78</v>
+        <v>227</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6112,10 +6277,10 @@
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>78</v>
@@ -6124,15 +6289,17 @@
         <v>78</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -6181,32 +6348,918 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH44" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AI43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
+      <c r="AI44" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AK43" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>78</v>
+      <c r="AK44" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="P49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>387</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM43">
+  <autoFilter ref="A1:AM51">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -6216,7 +7269,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI42">
+  <conditionalFormatting sqref="A2:AI50">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Communication.xlsx
+++ b/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Communication.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2028-04-01</t>
+    <t>2026-06-30</t>
   </si>
   <si>
     <t>Publisher</t>
